--- a/storage/exports/barras3.xlsx
+++ b/storage/exports/barras3.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="190">
   <si>
     <t>lpn</t>
   </si>
@@ -233,7 +233,7 @@
     <t>500000137190860001</t>
   </si>
   <si>
-    <t>2</t>
+    <t>579</t>
   </si>
   <si>
     <t>13719086</t>
@@ -257,15 +257,9 @@
     <t>500000137190860002</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>500000137190860003</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>780</t>
   </si>
   <si>
@@ -275,7 +269,7 @@
     <t>500000137190860004</t>
   </si>
   <si>
-    <t>5</t>
+    <t>573</t>
   </si>
   <si>
     <t>13718761</t>
@@ -296,307 +290,289 @@
     <t>500000137190860005</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>500000137190860006</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>500000137190860007</t>
   </si>
   <si>
+    <t>500000137190860008</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
-    <t>500000137190860008</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>200</t>
+    <t>058</t>
+  </si>
+  <si>
+    <t>0000009853058</t>
+  </si>
+  <si>
+    <t>BELL-S-ARROZ-EXTRA-ANEJO-BL750GR</t>
+  </si>
+  <si>
+    <t>1275</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>500000137190860009</t>
+  </si>
+  <si>
+    <t>676</t>
+  </si>
+  <si>
+    <t>0000009923676</t>
+  </si>
+  <si>
+    <t>BELL-S-ARROZ-SUPERIOR-BL750GR</t>
+  </si>
+  <si>
+    <t>500000137190860010</t>
+  </si>
+  <si>
+    <t>500000137190860011</t>
+  </si>
+  <si>
+    <t>570</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>500000137190860012</t>
+  </si>
+  <si>
+    <t>659</t>
+  </si>
+  <si>
+    <t>2200000062659</t>
+  </si>
+  <si>
+    <t>BELL-S-ARROZ-INTEGRAL-BL5KG</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>500000137190860013</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>500000137190860014</t>
+  </si>
+  <si>
+    <t>500000137190860015</t>
+  </si>
+  <si>
+    <t>500000137190860016</t>
+  </si>
+  <si>
+    <t>500000137190860017</t>
+  </si>
+  <si>
+    <t>500000137190860018</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>7753938009326</t>
+  </si>
+  <si>
+    <t>ARO-ARROZ-EXTRA-ANEJO-X5KG</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>500000137190860019</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>7753938009371</t>
+  </si>
+  <si>
+    <t>ARO-ARROZ-SUPERIOR-ANEJO-X5KG</t>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>7753938009357</t>
+  </si>
+  <si>
+    <t>ARO-ARROZ-DESPUNTADO-NIR-SC10KG</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>0000009853058</t>
-  </si>
-  <si>
-    <t>BELL-S-ARROZ-EXTRA-ANEJO-BL750GR</t>
-  </si>
-  <si>
-    <t>1275</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>500000137190860009</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>0000009923676</t>
-  </si>
-  <si>
-    <t>BELL-S-ARROZ-SUPERIOR-BL750GR</t>
-  </si>
-  <si>
-    <t>500000137190860010</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>500000137190860011</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>570</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>500000137190860012</t>
+    <t>500000137190860020</t>
+  </si>
+  <si>
+    <t>098</t>
+  </si>
+  <si>
+    <t>7757018000098</t>
+  </si>
+  <si>
+    <t>GRAN-CHALAN-ARROZ-EXTRA-GOURMET-BL5KG</t>
+  </si>
+  <si>
+    <t>500000137190860021</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>500000137190860022</t>
+  </si>
+  <si>
+    <t>555</t>
+  </si>
+  <si>
+    <t>7757018000555</t>
+  </si>
+  <si>
+    <t>SOMOS-DEL-NORTE-ARROZ-INTEGRAL-650GR</t>
+  </si>
+  <si>
+    <t>1350</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>500000137190860023</t>
+  </si>
+  <si>
+    <t>420</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>2200000062659</t>
-  </si>
-  <si>
-    <t>BELL-S-ARROZ-INTEGRAL-BL5KG</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>500000137190860013</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>185</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>500000137190860014</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>500000137190860015</t>
+    <t>500000137190860024</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>7757018000500</t>
+  </si>
+  <si>
+    <t>SOMOS-DEL-NORTE-ARROZ-SUPERIOR-650GR</t>
+  </si>
+  <si>
+    <t>500000137190860025</t>
+  </si>
+  <si>
+    <t>510</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>500000137190860016</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>500000137190860017</t>
-  </si>
-  <si>
-    <t>500000137190860018</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>7753938009326</t>
-  </si>
-  <si>
-    <t>ARO-ARROZ-EXTRA-ANEJO-X5KG</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>500000137190860019</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>7753938009371</t>
-  </si>
-  <si>
-    <t>ARO-ARROZ-SUPERIOR-ANEJO-X5KG</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>7753938009357</t>
-  </si>
-  <si>
-    <t>ARO-ARROZ-DESPUNTADO-NIR-SC10KG</t>
-  </si>
-  <si>
-    <t>500000137190860020</t>
+    <t>531</t>
+  </si>
+  <si>
+    <t>7757018000531</t>
+  </si>
+  <si>
+    <t>SOMOS-DEL-NORTE-ARROZ-FAMILIAR-BL-650GR</t>
+  </si>
+  <si>
+    <t>840</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>500000137190860026</t>
+  </si>
+  <si>
+    <t>487</t>
+  </si>
+  <si>
+    <t>7757018000487</t>
+  </si>
+  <si>
+    <t>SOMOS-DEL-NORTE-ARROZ-EXTRA-BL-650GR</t>
+  </si>
+  <si>
+    <t>500000137190860027</t>
+  </si>
+  <si>
+    <t>1110</t>
+  </si>
+  <si>
+    <t>500000137190860028</t>
+  </si>
+  <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>7757018000081</t>
+  </si>
+  <si>
+    <t>GRAN-CHALAN-GOURMET-EXTRA-ANEJO-X-10-KG</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>500000137190860029</t>
+  </si>
+  <si>
+    <t>500000137190860030</t>
+  </si>
+  <si>
+    <t>500000137190860031</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>500000137190860032</t>
+  </si>
+  <si>
+    <t>623</t>
+  </si>
+  <si>
+    <t>7757018000623</t>
+  </si>
+  <si>
+    <t>GRAN-CHALAN-ARROZ-SUPERIOR-ANEJO-750-GR</t>
+  </si>
+  <si>
+    <t>690</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>7757018000098</t>
-  </si>
-  <si>
-    <t>GRAN-CHALAN-ARROZ-EXTRA-GOURMET-BL5KG</t>
-  </si>
-  <si>
-    <t>500000137190860021</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>500000137190860022</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>7757018000555</t>
-  </si>
-  <si>
-    <t>SOMOS-DEL-NORTE-ARROZ-INTEGRAL-650GR</t>
-  </si>
-  <si>
-    <t>1350</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>500000137190860023</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>500000137190860024</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>7757018000500</t>
-  </si>
-  <si>
-    <t>SOMOS-DEL-NORTE-ARROZ-SUPERIOR-650GR</t>
-  </si>
-  <si>
-    <t>500000137190860025</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>510</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>7757018000531</t>
-  </si>
-  <si>
-    <t>SOMOS-DEL-NORTE-ARROZ-FAMILIAR-BL-650GR</t>
-  </si>
-  <si>
-    <t>840</t>
-  </si>
-  <si>
-    <t>500000137190860026</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>7757018000487</t>
-  </si>
-  <si>
-    <t>SOMOS-DEL-NORTE-ARROZ-EXTRA-BL-650GR</t>
-  </si>
-  <si>
-    <t>500000137190860027</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>1110</t>
-  </si>
-  <si>
-    <t>500000137190860028</t>
-  </si>
-  <si>
-    <t>7757018000081</t>
-  </si>
-  <si>
-    <t>GRAN-CHALAN-GOURMET-EXTRA-ANEJO-X-10-KG</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>500000137190860029</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>500000137190860030</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>500000137190860031</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>500000137190860032</t>
-  </si>
-  <si>
-    <t>7757018000623</t>
-  </si>
-  <si>
-    <t>GRAN-CHALAN-ARROZ-SUPERIOR-ANEJO-750-GR</t>
-  </si>
-  <si>
-    <t>690</t>
-  </si>
-  <si>
     <t>500000137190860033</t>
+  </si>
+  <si>
+    <t>739</t>
   </si>
   <si>
     <t>7757018000739</t>
@@ -1339,7 +1315,7 @@
         <v>79</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
         <v>73</v>
@@ -1425,10 +1401,10 @@
     </row>
     <row r="4" spans="1:71">
       <c r="A4" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
         <v>73</v>
@@ -1443,10 +1419,10 @@
         <v>76</v>
       </c>
       <c r="G4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I4"/>
       <c r="J4"/>
@@ -1514,28 +1490,28 @@
     </row>
     <row r="5" spans="1:71">
       <c r="A5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
         <v>85</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="E5" t="s">
         <v>75</v>
       </c>
       <c r="F5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" t="s">
         <v>89</v>
-      </c>
-      <c r="G5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H5" t="s">
-        <v>91</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -1603,28 +1579,28 @@
     </row>
     <row r="6" spans="1:71">
       <c r="A6" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>75</v>
       </c>
       <c r="F6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" t="s">
         <v>89</v>
-      </c>
-      <c r="G6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H6" t="s">
-        <v>91</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -1692,28 +1668,28 @@
     </row>
     <row r="7" spans="1:71">
       <c r="A7" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>75</v>
       </c>
       <c r="F7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" t="s">
         <v>89</v>
-      </c>
-      <c r="G7" t="s">
-        <v>90</v>
-      </c>
-      <c r="H7" t="s">
-        <v>91</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1781,28 +1757,28 @@
     </row>
     <row r="8" spans="1:71">
       <c r="A8" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>75</v>
       </c>
       <c r="F8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" t="s">
         <v>89</v>
-      </c>
-      <c r="G8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H8" t="s">
-        <v>91</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -1870,49 +1846,49 @@
     </row>
     <row r="9" spans="1:71">
       <c r="A9" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>75</v>
       </c>
       <c r="F9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" t="s">
+        <v>85</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="I9" t="s">
-        <v>101</v>
-      </c>
-      <c r="J9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="L9" t="s">
         <v>75</v>
       </c>
       <c r="M9" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="N9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="O9" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="P9"/>
       <c r="Q9"/>
@@ -1973,22 +1949,22 @@
     </row>
     <row r="10" spans="1:71">
       <c r="A10" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
         <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G10" t="s">
         <v>77</v>
@@ -2062,22 +2038,22 @@
     </row>
     <row r="11" spans="1:71">
       <c r="A11" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
         <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G11" t="s">
         <v>77</v>
@@ -2151,28 +2127,28 @@
     </row>
     <row r="12" spans="1:71">
       <c r="A12" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B12" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
         <v>75</v>
       </c>
       <c r="F12" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G12" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="H12" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -2240,28 +2216,28 @@
     </row>
     <row r="13" spans="1:71">
       <c r="A13" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
         <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G13" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -2329,28 +2305,28 @@
     </row>
     <row r="14" spans="1:71">
       <c r="A14" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
         <v>75</v>
       </c>
       <c r="F14" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G14" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="H14" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -2418,28 +2394,28 @@
     </row>
     <row r="15" spans="1:71">
       <c r="A15" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E15" t="s">
         <v>75</v>
       </c>
       <c r="F15" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G15" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -2507,28 +2483,28 @@
     </row>
     <row r="16" spans="1:71">
       <c r="A16" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="B16" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E16" t="s">
         <v>75</v>
       </c>
       <c r="F16" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G16" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -2596,28 +2572,28 @@
     </row>
     <row r="17" spans="1:71">
       <c r="A17" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B17" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E17" t="s">
         <v>75</v>
       </c>
       <c r="F17" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G17" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -2685,28 +2661,28 @@
     </row>
     <row r="18" spans="1:71">
       <c r="A18" s="1" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E18" t="s">
         <v>75</v>
       </c>
       <c r="F18" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G18" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -2774,28 +2750,28 @@
     </row>
     <row r="19" spans="1:71">
       <c r="A19" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B19" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
         <v>75</v>
       </c>
       <c r="F19" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="G19" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="H19" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -2863,49 +2839,49 @@
     </row>
     <row r="20" spans="1:71">
       <c r="A20" s="1" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B20" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="E20" t="s">
         <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G20" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="H20" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="I20" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="J20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="L20" t="s">
         <v>75</v>
       </c>
       <c r="M20" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="N20" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="O20" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="P20"/>
       <c r="Q20"/>
@@ -2966,28 +2942,28 @@
     </row>
     <row r="21" spans="1:71">
       <c r="A21" s="1" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E21" t="s">
         <v>75</v>
       </c>
       <c r="F21" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G21" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -3055,28 +3031,28 @@
     </row>
     <row r="22" spans="1:71">
       <c r="A22" s="1" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="B22" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E22" t="s">
         <v>75</v>
       </c>
       <c r="F22" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G22" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="H22" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
@@ -3144,28 +3120,28 @@
     </row>
     <row r="23" spans="1:71">
       <c r="A23" s="1" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E23" t="s">
         <v>75</v>
       </c>
       <c r="F23" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G23" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="H23" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
@@ -3233,28 +3209,28 @@
     </row>
     <row r="24" spans="1:71">
       <c r="A24" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E24" t="s">
         <v>75</v>
       </c>
       <c r="F24" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G24" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="H24" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
@@ -3322,28 +3298,28 @@
     </row>
     <row r="25" spans="1:71">
       <c r="A25" s="1" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B25" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E25" t="s">
         <v>75</v>
       </c>
       <c r="F25" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="G25" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="H25" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
@@ -3411,49 +3387,49 @@
     </row>
     <row r="26" spans="1:71">
       <c r="A26" s="1" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E26" t="s">
         <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="G26" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="H26" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="I26" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="J26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="L26" t="s">
         <v>75</v>
       </c>
       <c r="M26" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="O26" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="P26"/>
       <c r="Q26"/>
@@ -3514,28 +3490,28 @@
     </row>
     <row r="27" spans="1:71">
       <c r="A27" s="1" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B27" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E27" t="s">
         <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G27" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="H27" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="I27"/>
       <c r="J27"/>
@@ -3603,28 +3579,28 @@
     </row>
     <row r="28" spans="1:71">
       <c r="A28" s="1" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B28" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="C28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E28" t="s">
         <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G28" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H28" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="I28"/>
       <c r="J28"/>
@@ -3692,28 +3668,28 @@
     </row>
     <row r="29" spans="1:71">
       <c r="A29" s="1" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="B29" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E29" t="s">
         <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="G29" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="H29" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I29"/>
       <c r="J29"/>
@@ -3781,28 +3757,28 @@
     </row>
     <row r="30" spans="1:71">
       <c r="A30" s="1" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B30" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E30" t="s">
         <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="G30" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="H30" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I30"/>
       <c r="J30"/>
@@ -3870,28 +3846,28 @@
     </row>
     <row r="31" spans="1:71">
       <c r="A31" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B31" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="C31" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E31" t="s">
         <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="G31" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="H31" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I31"/>
       <c r="J31"/>
@@ -3959,28 +3935,28 @@
     </row>
     <row r="32" spans="1:71">
       <c r="A32" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B32" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E32" t="s">
         <v>75</v>
       </c>
       <c r="F32" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="G32" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="H32" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="I32"/>
       <c r="J32"/>
@@ -4048,28 +4024,28 @@
     </row>
     <row r="33" spans="1:71">
       <c r="A33" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="E33" t="s">
         <v>75</v>
       </c>
       <c r="F33" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="G33" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="H33" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="I33"/>
       <c r="J33"/>
@@ -4137,28 +4113,28 @@
     </row>
     <row r="34" spans="1:71">
       <c r="A34" s="1" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="E34" t="s">
         <v>75</v>
       </c>
       <c r="F34" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="G34" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="H34" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="I34"/>
       <c r="J34"/>
